--- a/data/trans_orig/IP07C01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C01-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>32916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23661</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>29967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44301</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>26164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42503</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34439</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79615</t>
+          <t>79005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99056</t>
+          <t>99380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>45381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59009</t>
+          <t>59261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78904</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>458</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50865</t>
+          <t>51539</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68689</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>35204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>53187</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>512</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24498</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43770</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>124341</t>
+          <t>124459</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>150260</t>
+          <t>150093</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>141891</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>170612</t>
+          <t>169148</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>273430</t>
+          <t>274278</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>311794</t>
+          <t>313927</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>99813</t>
+          <t>99756</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125767</t>
+          <t>124716</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>109003</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>135400</t>
+          <t>136754</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>214679</t>
+          <t>216167</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>253568</t>
+          <t>255330</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20607</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>30730</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44394</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37207</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29980</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>45221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52207</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65079</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87345</t>
+          <t>86689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40109</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>55135</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52323</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>80725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>104250</t>
+          <t>103805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47219</t>
+          <t>47826</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37361</t>
+          <t>36475</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31713</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46002</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72905</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92566</t>
+          <t>92397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>93224</t>
+          <t>92095</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>120039</t>
+          <t>118276</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>122734</t>
+          <t>124539</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>151451</t>
+          <t>152695</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>224440</t>
+          <t>223577</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>265165</t>
+          <t>262838</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>153492</t>
+          <t>154121</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>180992</t>
+          <t>182453</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>133315</t>
+          <t>132117</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>162001</t>
+          <t>161023</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>293595</t>
+          <t>295246</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>334258</t>
+          <t>334539</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10877,12 +10877,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -11431,12 +11431,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>31573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>44527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -12113,12 +12113,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>29980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43324</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12261,12 +12261,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -12795,12 +12795,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>44621</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63559</t>
+          <t>62852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44633</t>
+          <t>45478</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>62179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95436</t>
+          <t>95239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119056</t>
+          <t>119340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>45838</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74019</t>
+          <t>74212</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>98264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13169,12 +13169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13287,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -13477,12 +13477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>60745</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>80418</t>
+          <t>79818</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -13590,12 +13590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35668</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>56012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75919</t>
+          <t>75717</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13675,12 +13675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>35797</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48299</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -14272,12 +14272,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14307,12 +14307,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14400,12 +14400,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>155294</t>
+          <t>155426</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>185668</t>
+          <t>185641</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>163823</t>
+          <t>162404</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>194106</t>
+          <t>194220</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>328992</t>
+          <t>327894</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>371046</t>
+          <t>371916</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>120454</t>
+          <t>121006</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>113728</t>
+          <t>115103</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>144735</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>245030</t>
+          <t>245963</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>285537</t>
+          <t>287593</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15792,12 +15792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -15807,12 +15807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -15870,12 +15870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15920,12 +15920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15955,12 +15955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -16474,12 +16474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -16552,12 +16552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16602,12 +16602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16622,12 +16622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>16296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -17121,12 +17121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15039</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -17234,12 +17234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17249,12 +17249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17319,12 +17319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17417,12 +17417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -17803,12 +17803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59592</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47359</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17873,12 +17873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108101</t>
+          <t>109717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -17916,12 +17916,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34348</t>
+          <t>34089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17931,12 +17931,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17951,12 +17951,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -17966,12 +17966,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -17986,12 +17986,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67087</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -18485,12 +18485,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18520,12 +18520,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23633</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>46154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18555,12 +18555,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>42431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65912</t>
+          <t>67332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -18598,12 +18598,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18613,12 +18613,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>30965</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18648,12 +18648,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18668,12 +18668,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46002</t>
+          <t>44372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18683,12 +18683,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18726,12 +18726,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18761,12 +18761,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18796,12 +18796,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>834</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19217,12 +19217,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19237,12 +19237,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19252,12 +19252,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19315,12 +19315,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19365,12 +19365,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -19849,12 +19849,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>107949</t>
+          <t>106714</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>160158</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>127351</t>
+          <t>128570</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>165743</t>
+          <t>165118</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19899,12 +19899,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19919,12 +19919,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>246693</t>
+          <t>245303</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>306787</t>
+          <t>307064</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19934,12 +19934,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>84110</t>
+          <t>83905</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,12 +19977,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>82798</t>
+          <t>82422</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>117899</t>
+          <t>118517</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>138696</t>
+          <t>137470</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>192931</t>
+          <t>191064</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20790</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
